--- a/docs/Этапы_подготовки_учебного_центра.xlsx
+++ b/docs/Этапы_подготовки_учебного_центра.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Этапы подготовки центра" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Этапы подготовки центра'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Этапы подготовки центра'!$A$1:$V$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,48 +31,41 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001F4E79"/>
-      <sz val="18"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="004A5563"/>
-      <sz val="10"/>
+      <sz val="7"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="7"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00222222"/>
-      <sz val="11"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="00222222"/>
-      <sz val="11"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="12"/>
+      <color rgb="00222222"/>
+      <sz val="7"/>
     </font>
   </fonts>
   <fills count="11">
@@ -154,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -205,21 +198,15 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -585,49 +572,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="68" customWidth="1" min="6" max="6"/>
-    <col width="4.2" customWidth="1" min="7" max="7"/>
-    <col width="4.2" customWidth="1" min="8" max="8"/>
-    <col width="4.2" customWidth="1" min="9" max="9"/>
-    <col width="4.2" customWidth="1" min="10" max="10"/>
-    <col width="4.2" customWidth="1" min="11" max="11"/>
-    <col width="4.2" customWidth="1" min="12" max="12"/>
-    <col width="4.2" customWidth="1" min="13" max="13"/>
-    <col width="4.2" customWidth="1" min="14" max="14"/>
-    <col width="4.2" customWidth="1" min="15" max="15"/>
-    <col width="4.2" customWidth="1" min="16" max="16"/>
-    <col width="4.2" customWidth="1" min="17" max="17"/>
-    <col width="4.2" customWidth="1" min="18" max="18"/>
-    <col width="4.2" customWidth="1" min="19" max="19"/>
-    <col width="4.2" customWidth="1" min="20" max="20"/>
-    <col width="4.2" customWidth="1" min="21" max="21"/>
-    <col width="4.2" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+    <col width="3" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="16" max="16"/>
+    <col width="3" customWidth="1" min="17" max="17"/>
+    <col width="3" customWidth="1" min="18" max="18"/>
+    <col width="3" customWidth="1" min="19" max="19"/>
+    <col width="3" customWidth="1" min="20" max="20"/>
+    <col width="3" customWidth="1" min="21" max="21"/>
+    <col width="3" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Этапы подготовки учебного центра</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Неделя 1 — первая неделя работ. Полоса — ориентир по длительности: для «от …» взята нижняя граница, для «до 2 недель» — две недели, для устава — две недели (верхняя граница 14 календарных дней). Этапы 1–6 и лицензия начинаются параллельно. Заявление подаётся после закрытия этапов 2–6, на графике это недели 5–6. Настройка администрирования — неделя 7. Запуск показан с недели 8 и продолжается дальше. Для лицензии на графике отложены 12 недель (3 месяца); фактический срок зависит от комплекта документов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="22" customHeight="1">
+          <t>Неделя 1 — старт работ. Этапы 1–6 и лицензия идут параллельно. Заявление — недели 5–6, после закрытия этапов 2–6. Настройка администрирования — неделя 7. Запуск — с недели 8 и далее. Лицензия на графике — 12 недель.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1"/>
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>№</t>
@@ -640,17 +627,17 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Длительность этапа</t>
+          <t>Длительность</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Начало, неделя</t>
+          <t>Начало</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Окончание, неделя</t>
+          <t>Окончание</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -679,7 +666,7 @@
       <c r="U4" s="5" t="n"/>
       <c r="V4" s="5" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
@@ -735,7 +722,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" ht="82" customHeight="1">
+    <row r="6" ht="61" customHeight="1">
       <c r="A6" s="7" t="n">
         <v>1</v>
       </c>
@@ -779,7 +766,7 @@
       <c r="U6" s="11" t="n"/>
       <c r="V6" s="11" t="n"/>
     </row>
-    <row r="7" ht="118" customHeight="1">
+    <row r="7" ht="94" customHeight="1">
       <c r="A7" s="12" t="n">
         <v>2</v>
       </c>
@@ -823,7 +810,7 @@
       <c r="U7" s="11" t="n"/>
       <c r="V7" s="11" t="n"/>
     </row>
-    <row r="8" ht="82" customHeight="1">
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" s="7" t="n">
         <v>3</v>
       </c>
@@ -867,7 +854,7 @@
       <c r="U8" s="11" t="n"/>
       <c r="V8" s="11" t="n"/>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="39" customHeight="1">
       <c r="A9" s="12" t="n">
         <v>4</v>
       </c>
@@ -911,7 +898,7 @@
       <c r="U9" s="11" t="n"/>
       <c r="V9" s="11" t="n"/>
     </row>
-    <row r="10" ht="64" customHeight="1">
+    <row r="10" ht="39" customHeight="1">
       <c r="A10" s="7" t="n">
         <v>5</v>
       </c>
@@ -955,7 +942,7 @@
       <c r="U10" s="11" t="n"/>
       <c r="V10" s="11" t="n"/>
     </row>
-    <row r="11" ht="82" customHeight="1">
+    <row r="11" ht="61" customHeight="1">
       <c r="A11" s="12" t="n">
         <v>6</v>
       </c>
@@ -999,7 +986,7 @@
       <c r="U11" s="11" t="n"/>
       <c r="V11" s="11" t="n"/>
     </row>
-    <row r="12" ht="64" customHeight="1">
+    <row r="12" ht="39" customHeight="1">
       <c r="A12" s="7" t="n">
         <v>7</v>
       </c>
@@ -1043,7 +1030,7 @@
       <c r="U12" s="11" t="n"/>
       <c r="V12" s="11" t="n"/>
     </row>
-    <row r="13" ht="100" customHeight="1">
+    <row r="13" ht="72" customHeight="1">
       <c r="A13" s="12" t="n">
         <v>8</v>
       </c>
@@ -1087,7 +1074,7 @@
       <c r="U13" s="11" t="n"/>
       <c r="V13" s="11" t="n"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="7" t="n">
         <v>9</v>
       </c>
@@ -1135,7 +1122,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1">
+    <row r="15" ht="39" customHeight="1">
       <c r="A15" s="12" t="n">
         <v>10</v>
       </c>
@@ -1179,57 +1166,16 @@
       <c r="U15" s="11" t="n"/>
       <c r="V15" s="11" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="16" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>Обозначения</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="21" t="inlineStr"/>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>Подготовка, параллельно с недели 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="23" t="inlineStr"/>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>Заявление и включение в реестр</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="24" t="inlineStr"/>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>Настройка администрирования</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="25" t="inlineStr"/>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>Запуск, далее постоянно</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="26" t="inlineStr"/>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>Лицензия на ДПО, параллельно</t>
+          <t>Цвета: голубой — подготовка; тёмно-синий — заявление; синий — настройка администрирования; зелёный — запуск, далее постоянно; оранжевый — лицензия на ДПО, параллельно.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="10">
     <mergeCell ref="A2:V2"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="A4:A5"/>
@@ -1237,18 +1183,14 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A17:V17"/>
     <mergeCell ref="G4:V4"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B20:D20"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="2" fitToWidth="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.3" header="0.15" footer="0.15"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LЭтапы подготовки учебного центра</oddHeader>
-    <oddFooter>&amp;RСтраница &amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CЭтапы подготовки учебного центра</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/docs/Этапы_подготовки_учебного_центра.xlsx
+++ b/docs/Этапы_подготовки_учебного_центра.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Этапы подготовки центра" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Этапы подготовки центра'!$A$1:$V$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Этапы подготовки центра'!$A$1:$V$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,12 +32,6 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="004A5563"/>
-      <sz val="7"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -61,11 +55,6 @@
       <name val="Calibri"/>
       <color rgb="00222222"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00222222"/>
-      <sz val="7"/>
     </font>
   </fonts>
   <fills count="11">
@@ -147,48 +136,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -198,14 +184,11 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -572,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -606,595 +589,571 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Неделя 1 — старт работ. Этапы 1–6 и лицензия идут параллельно. Заявление — недели 5–6, после закрытия этапов 2–6. Настройка администрирования — неделя 7. Запуск — с недели 8 и далее. Лицензия на графике — 12 недель.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="4" customHeight="1"/>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="2" ht="4" customHeight="1"/>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Длительность</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Начало</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Окончание</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Комментарии</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Недели проекта</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
-      <c r="P4" s="5" t="n"/>
-      <c r="Q4" s="5" t="n"/>
-      <c r="R4" s="5" t="n"/>
-      <c r="S4" s="5" t="n"/>
-      <c r="T4" s="5" t="n"/>
-      <c r="U4" s="5" t="n"/>
-      <c r="V4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="6" t="n">
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+      <c r="P3" s="4" t="n"/>
+      <c r="Q3" s="4" t="n"/>
+      <c r="R3" s="4" t="n"/>
+      <c r="S3" s="4" t="n"/>
+      <c r="T3" s="4" t="n"/>
+      <c r="U3" s="4" t="n"/>
+      <c r="V3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K4" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M4" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="N4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="O4" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="P4" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="Q4" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="R4" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="S4" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="T4" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="U4" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="V4" s="5" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="6" ht="61" customHeight="1">
-      <c r="A6" s="7" t="n">
+    <row r="5" ht="61" customHeight="1">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Внесение изменений в устав в части вида деятельности</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>7–14 календарных дней</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>По подпункту «а» пункта 5 Требований, утверждённых постановлением Правительства РФ от 16.12.2021 № 2334, в учредительных документах организации указывают вид услуг в области охраны труда, для оказания которых нужна аккредитация.</t>
         </is>
       </c>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="11" t="n"/>
-      <c r="P6" s="11" t="n"/>
-      <c r="Q6" s="11" t="n"/>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="11" t="n"/>
-      <c r="T6" s="11" t="n"/>
-      <c r="U6" s="11" t="n"/>
-      <c r="V6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="94" customHeight="1">
-      <c r="A7" s="12" t="n">
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="10" t="n"/>
+      <c r="V5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="94" customHeight="1">
+      <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Помещение и материально-техническая база</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>от 2 недель</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>При готовом помещении и материально-технической базе проводится проверка полноты оснащения под реализацию программ. Если нужно обучение на высоте, необходимо закупить и установить полигон для отработки практических навыков либо заключить договор аренды. Запуск можно вести параллельно: начать обучение по основным программам, а обучение на высоте подключить по готовности полигона.</t>
         </is>
       </c>
-      <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n"/>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="n"/>
-      <c r="P7" s="11" t="n"/>
-      <c r="Q7" s="11" t="n"/>
-      <c r="R7" s="11" t="n"/>
-      <c r="S7" s="11" t="n"/>
-      <c r="T7" s="11" t="n"/>
-      <c r="U7" s="11" t="n"/>
-      <c r="V7" s="11" t="n"/>
-    </row>
-    <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="7" t="n">
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="10" t="n"/>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Подготовка преподавателей и членов комиссии по проверке знаний</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>до 2 недель</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Возможно, имеется подготовленный персонал, обученный по необходимым программам для формирования комиссии. Необходимо не менее двух преподавателей по каждой программе; это могут быть одни и те же люди. Общее количество членов комиссии — не менее трёх.</t>
         </is>
       </c>
-      <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
-      <c r="N8" s="11" t="n"/>
-      <c r="O8" s="11" t="n"/>
-      <c r="P8" s="11" t="n"/>
-      <c r="Q8" s="11" t="n"/>
-      <c r="R8" s="11" t="n"/>
-      <c r="S8" s="11" t="n"/>
-      <c r="T8" s="11" t="n"/>
-      <c r="U8" s="11" t="n"/>
-      <c r="V8" s="11" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="39" customHeight="1">
+      <c r="A8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Программы и материалы проверки знания</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>от 4 недель</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Разработать и утвердить по каждому виду программу, учебно-методические материалы и материалы для проверки знания.</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="10" t="n"/>
     </row>
     <row r="9" ht="39" customHeight="1">
-      <c r="A9" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Программы и материалы проверки знания</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>от 4 недель</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Разработка положения об учебном центре, учёте документов и персональных данных</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>от 2 недель</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Разработать и утвердить по каждому виду программу, учебно-методические материалы и материалы для проверки знания.</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Дополнительно оформить шаблоны договоров, форм заявок, протоколов и журналов.</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="10" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="n"/>
-      <c r="P9" s="11" t="n"/>
-      <c r="Q9" s="11" t="n"/>
-      <c r="R9" s="11" t="n"/>
-      <c r="S9" s="11" t="n"/>
-      <c r="T9" s="11" t="n"/>
-      <c r="U9" s="11" t="n"/>
-      <c r="V9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="39" customHeight="1">
-      <c r="A10" s="7" t="n">
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="61" customHeight="1">
+      <c r="A10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Сайт, справочная база и дистанционное обучение</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>от 4 недель</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>В случае применения дистанционного формата нужна система обучения на основании постановления Правительства РФ от 16.12.2021 № 2334. Возможно приобретение готовых решений. Потребуется время на настройку и внедрение системы под процесс.</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="10" t="n"/>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n"/>
+      <c r="V10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="39" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Заявление на аккредитацию. Рассмотрение включения в реестр</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>2 недели</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Разработка положения об учебном центре, учёте документов и персональных данных</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>от 2 недель</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>Дополнительно оформить шаблоны договоров, форм заявок, протоколов и журналов.</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="11" t="n"/>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="11" t="n"/>
-      <c r="P10" s="11" t="n"/>
-      <c r="Q10" s="11" t="n"/>
-      <c r="R10" s="11" t="n"/>
-      <c r="S10" s="11" t="n"/>
-      <c r="T10" s="11" t="n"/>
-      <c r="U10" s="11" t="n"/>
-      <c r="V10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="61" customHeight="1">
-      <c r="A11" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Сайт, справочная база и дистанционное обучение</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>от 4 недель</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>В случае применения дистанционного формата нужна система обучения на основании постановления Правительства РФ от 16.12.2021 № 2334. Возможно приобретение готовых решений. Потребуется время на настройку и внедрение системы под процесс.</t>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Комплект собирать, когда устав зарегистрирован и закрыты этапы 2–6. Заявление подаётся через Госуслуги, без госпошлины, с подписью руководителя.</t>
         </is>
       </c>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n"/>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="10" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="n"/>
-      <c r="P11" s="11" t="n"/>
-      <c r="Q11" s="11" t="n"/>
-      <c r="R11" s="11" t="n"/>
-      <c r="S11" s="11" t="n"/>
-      <c r="T11" s="11" t="n"/>
-      <c r="U11" s="11" t="n"/>
-      <c r="V11" s="11" t="n"/>
-    </row>
-    <row r="12" ht="39" customHeight="1">
-      <c r="A12" s="7" t="n">
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n"/>
+      <c r="V11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Настройка администрирования процесса</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>1 неделя</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Заявление на аккредитацию. Рассмотрение включения в реестр</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>2 недели</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Комплект собирать, когда устав зарегистрирован и закрыты этапы 2–6. Заявление подаётся через Госуслуги, без госпошлины, с подписью руководителя.</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="11" t="n"/>
-      <c r="K12" s="15" t="n"/>
-      <c r="L12" s="15" t="n"/>
-      <c r="M12" s="11" t="n"/>
-      <c r="N12" s="11" t="n"/>
-      <c r="O12" s="11" t="n"/>
-      <c r="P12" s="11" t="n"/>
-      <c r="Q12" s="11" t="n"/>
-      <c r="R12" s="11" t="n"/>
-      <c r="S12" s="11" t="n"/>
-      <c r="T12" s="11" t="n"/>
-      <c r="U12" s="11" t="n"/>
-      <c r="V12" s="11" t="n"/>
-    </row>
-    <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="12" t="n">
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Регистрация заявок, учёт обучения, оформление протоколов и записей в реестре. Настройка кабинета учебного центра во ФГИС СОУТ. Возможно, потребуется система учёта. Как правило, готовые решения СДО не имеют необходимой системы учёта для конкретного процесса.</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="15" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="10" t="n"/>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
+      <c r="V12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Запуск работы учебного центра</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>постоянно</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Настройка администрирования процесса</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>1 неделя</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>Регистрация заявок, учёт обучения, оформление протоколов и записей в реестре. Настройка кабинета учебного центра во ФГИС СОУТ. Возможно, потребуется система учёта. Как правило, готовые решения СДО не имеют необходимой системы учёта для конкретного процесса.</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="16" t="n"/>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="11" t="n"/>
-      <c r="Q13" s="11" t="n"/>
-      <c r="R13" s="11" t="n"/>
-      <c r="S13" s="11" t="n"/>
-      <c r="T13" s="11" t="n"/>
-      <c r="U13" s="11" t="n"/>
-      <c r="V13" s="11" t="n"/>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Запуск работы учебного центра</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>постоянно</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>далее</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>При увеличении объёмов потребуется решение по автоматизации процесса.</t>
         </is>
       </c>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
-      <c r="N14" s="17" t="n"/>
-      <c r="O14" s="17" t="n"/>
-      <c r="P14" s="17" t="n"/>
-      <c r="Q14" s="17" t="n"/>
-      <c r="R14" s="17" t="n"/>
-      <c r="S14" s="17" t="n"/>
-      <c r="T14" s="17" t="n"/>
-      <c r="U14" s="17" t="n"/>
-      <c r="V14" s="18" t="inlineStr">
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="16" t="n"/>
+      <c r="O13" s="16" t="n"/>
+      <c r="P13" s="16" t="n"/>
+      <c r="Q13" s="16" t="n"/>
+      <c r="R13" s="16" t="n"/>
+      <c r="S13" s="16" t="n"/>
+      <c r="T13" s="16" t="n"/>
+      <c r="U13" s="16" t="n"/>
+      <c r="V13" s="17" t="inlineStr">
         <is>
           <t>→</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="39" customHeight="1">
-      <c r="A15" s="12" t="n">
+    <row r="14" ht="39" customHeight="1">
+      <c r="A14" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Лицензия на дополнительное профессиональное образование</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>несколько месяцев</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D14" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Нужна, когда центр ведёт повышение квалификации и профессиональную переподготовку. Этот контур идёт параллельно и срок аккредитации не сдвигает.</t>
         </is>
       </c>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="19" t="n"/>
-      <c r="I15" s="19" t="n"/>
-      <c r="J15" s="19" t="n"/>
-      <c r="K15" s="19" t="n"/>
-      <c r="L15" s="19" t="n"/>
-      <c r="M15" s="19" t="n"/>
-      <c r="N15" s="19" t="n"/>
-      <c r="O15" s="19" t="n"/>
-      <c r="P15" s="19" t="n"/>
-      <c r="Q15" s="19" t="n"/>
-      <c r="R15" s="19" t="n"/>
-      <c r="S15" s="11" t="n"/>
-      <c r="T15" s="11" t="n"/>
-      <c r="U15" s="11" t="n"/>
-      <c r="V15" s="11" t="n"/>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>Цвета: голубой — подготовка; тёмно-синий — заявление; синий — настройка администрирования; зелёный — запуск, далее постоянно; оранжевый — лицензия на ДПО, параллельно.</t>
-        </is>
-      </c>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="18" t="n"/>
+      <c r="M14" s="18" t="n"/>
+      <c r="N14" s="18" t="n"/>
+      <c r="O14" s="18" t="n"/>
+      <c r="P14" s="18" t="n"/>
+      <c r="Q14" s="18" t="n"/>
+      <c r="R14" s="18" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A17:V17"/>
-    <mergeCell ref="G4:V4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="G3:V3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.3" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;CЭтапы подготовки учебного центра</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
--- a/docs/Этапы_подготовки_учебного_центра.xlsx
+++ b/docs/Этапы_подготовки_учебного_центра.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Этапы подготовки центра" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Этапы подготовки центра'!$A$1:$V$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Этапы подготовки центра'!$A$1:$V$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +55,11 @@
       <name val="Calibri"/>
       <color rgb="00222222"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="7"/>
     </font>
   </fonts>
   <fills count="11">
@@ -136,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -189,6 +194,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1142,8 +1150,16 @@
       <c r="U14" s="10" t="n"/>
       <c r="V14" s="10" t="n"/>
     </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Цвета: голубой — подготовка; тёмно-синий — заявление; синий — настройка администрирования; зелёный — запуск, далее постоянно; оранжевый — лицензия на ДПО, параллельно.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A16:V16"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A3:A4"/>
@@ -1155,5 +1171,13 @@
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.3" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CЭтапы подготовки учебного центра</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/docs/Этапы_подготовки_учебного_центра.xlsx
+++ b/docs/Этапы_подготовки_учебного_центра.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Этапы подготовки центра" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Этапы подготовки центра'!$A$1:$V$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Этапы подготовки центра'!$A$1:$V$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,11 +55,6 @@
       <name val="Calibri"/>
       <color rgb="00222222"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00222222"/>
-      <sz val="7"/>
     </font>
   </fonts>
   <fills count="11">
@@ -141,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -194,9 +189,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -563,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1150,16 +1142,8 @@
       <c r="U14" s="10" t="n"/>
       <c r="V14" s="10" t="n"/>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>Цвета: голубой — подготовка; тёмно-синий — заявление; синий — настройка администрирования; зелёный — запуск, далее постоянно; оранжевый — лицензия на ДПО, параллельно.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A16:V16"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A3:A4"/>
@@ -1171,13 +1155,5 @@
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.35" bottom="0.3" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;CЭтапы подготовки учебного центра</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>